--- a/data/EVALUACIONES/PESO/PESO.xlsx
+++ b/data/EVALUACIONES/PESO/PESO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30415"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\PESO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F65EBB-E3AC-47E3-89DA-673FB22AC8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{07F65EBB-E3AC-47E3-89DA-673FB22AC8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73E7D347-9227-4663-AC17-34C11335579F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Fecha</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>Ikki_Muller_Salak</t>
-  </si>
-  <si>
-    <t>Alejandro_Garcia_Gumiel</t>
   </si>
   <si>
     <t>Rodri_Sanchez_Ramos</t>
@@ -178,8 +175,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{20BA1720-C6BF-4B1C-B0CE-F8976D0E923F}" name="Tabla2" displayName="Tabla2" ref="A1:C29" totalsRowShown="0">
-  <autoFilter ref="A1:C29" xr:uid="{20BA1720-C6BF-4B1C-B0CE-F8976D0E923F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{20BA1720-C6BF-4B1C-B0CE-F8976D0E923F}" name="Tabla2" displayName="Tabla2" ref="A1:C28" totalsRowShown="0">
+  <autoFilter ref="A1:C28" xr:uid="{20BA1720-C6BF-4B1C-B0CE-F8976D0E923F}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{82DE221A-A8AD-47E7-BFF8-F22FC2A6BF88}" name="Fecha" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{1D1E7BB7-BFD6-4163-9238-19F72ED2954E}" name="Nombre"/>
@@ -452,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -476,7 +473,7 @@
         <v>46247</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>65.599999999999994</v>
@@ -487,7 +484,7 @@
         <v>46247</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>66.7</v>
@@ -498,7 +495,7 @@
         <v>46247</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>62.2</v>
@@ -509,7 +506,7 @@
         <v>46247</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>78.8</v>
@@ -520,7 +517,7 @@
         <v>46247</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>68.900000000000006</v>
@@ -542,7 +539,7 @@
         <v>46247</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8">
         <v>60.1</v>
@@ -553,7 +550,7 @@
         <v>46247</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>79.599999999999994</v>
@@ -564,7 +561,7 @@
         <v>46247</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10">
         <v>71.7</v>
@@ -586,7 +583,7 @@
         <v>46247</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12">
         <v>75.3</v>
@@ -597,7 +594,7 @@
         <v>46247</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>68.400000000000006</v>
@@ -619,7 +616,7 @@
         <v>46247</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15">
         <v>71.900000000000006</v>
@@ -630,7 +627,7 @@
         <v>46247</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16">
         <v>87.3</v>
@@ -641,7 +638,7 @@
         <v>46247</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17">
         <v>62.7</v>
@@ -652,7 +649,7 @@
         <v>46247</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18">
         <v>75</v>
@@ -674,7 +671,7 @@
         <v>46247</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20">
         <v>66.099999999999994</v>
@@ -685,10 +682,10 @@
         <v>46247</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C21">
-        <v>71</v>
+        <v>81.900000000000006</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -696,10 +693,10 @@
         <v>46247</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C22">
-        <v>81.900000000000006</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -707,10 +704,10 @@
         <v>46247</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23">
-        <v>78.8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -718,10 +715,10 @@
         <v>46247</v>
       </c>
       <c r="B24" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C24">
-        <v>59</v>
+        <v>68.099999999999994</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -729,10 +726,10 @@
         <v>46247</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C25">
-        <v>68.099999999999994</v>
+        <v>80.900000000000006</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -740,10 +737,10 @@
         <v>46247</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C26">
-        <v>80.900000000000006</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -754,7 +751,7 @@
         <v>28</v>
       </c>
       <c r="C27">
-        <v>82</v>
+        <v>77.599999999999994</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -765,17 +762,6 @@
         <v>29</v>
       </c>
       <c r="C28">
-        <v>77.599999999999994</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>46247</v>
-      </c>
-      <c r="B29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29">
         <v>62</v>
       </c>
     </row>
